--- a/jogos_2025-03-13.xlsx
+++ b/jogos_2025-03-13.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,19 +643,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EGS Gafsa</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Sloboda Užice</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -669,80 +669,80 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="M2" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>3.69</v>
       </c>
       <c r="O2" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="R2" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="S2" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="T2" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="V2" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Z2" t="n">
         <v>1.48</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.25</v>
+        <v>4.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['46', '72']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AJ2" t="n">
         <v>2.75</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Tataouine</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -790,91 +790,91 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O3" t="n">
         <v>2</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="P3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>7</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['58']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['19', '71']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH3" t="n">
         <v>2.7</v>
       </c>
-      <c r="N3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O3" t="n">
-        <v>4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="T3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['81']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['21', '24']</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AI3" t="n">
-        <v>2.6</v>
+        <v>1.33</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.95</v>
+        <v>4.33</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45729.41666666666</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,19 +1030,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>EGS Gafsa</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sloboda Užice</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1056,80 +1056,80 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="M5" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>3.69</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="R5" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="S5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Y5" t="n">
         <v>2.4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.37</v>
       </c>
       <c r="Z5" t="n">
         <v>1.48</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.9</v>
+        <v>6.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.02</v>
+        <v>2.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['46', '72']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AJ5" t="n">
         <v>2.75</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tataouine</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.62</v>
+        <v>3.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="N6" t="n">
-        <v>5.6</v>
+        <v>2.3</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="S6" t="n">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="W6" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="X6" t="n">
-        <v>2.9</v>
+        <v>2.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.25</v>
+        <v>3.09</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>4</v>
+        <v>6.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['19', '71']</t>
+          <t>['21', '24']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.7</v>
+        <v>1.28</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.33</v>
+        <v>2.6</v>
       </c>
       <c r="AJ6" t="n">
-        <v>4.33</v>
+        <v>1.95</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45729.41666666666</v>
@@ -1942,100 +1942,100 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>['50', '86']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45729.54166666666</v>
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="M13" t="n">
         <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.99</v>
+        <v>2.78</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC13" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['25', '50']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ13" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>['33']</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45729.60416666666</v>
@@ -2191,81 +2191,81 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FeralpiSalò</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Clodiense</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>3</v>
       </c>
       <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.32</v>
+        <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>8.6</v>
+        <v>1.48</v>
       </c>
       <c r="O14" t="n">
-        <v>1.91</v>
+        <v>7</v>
       </c>
       <c r="P14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y14" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>8</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.75</v>
-      </c>
       <c r="Z14" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AA14" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AC14" t="n">
         <v>2.5</v>
@@ -2275,25 +2275,25 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['9', '59', '71']</t>
+          <t>['31', '33', '78']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>['18', '83']</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.06</v>
+        <v>2.65</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.4</v>
+        <v>1.09</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.25</v>
+        <v>4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>4.75</v>
+        <v>1.36</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45729.60416666666</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>FeralpiSalò</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Clodiense</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,55 +2346,55 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6.9</v>
+        <v>1.32</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="N15" t="n">
-        <v>1.48</v>
+        <v>8.6</v>
       </c>
       <c r="O15" t="n">
-        <v>7</v>
+        <v>1.91</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W15" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AA15" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AC15" t="n">
         <v>2.5</v>
@@ -2404,25 +2404,25 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['31', '33', '78']</t>
+          <t>['9', '59', '71']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['18', '83']</t>
+          <t>['83']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>2.65</v>
+        <v>1.06</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.09</v>
+        <v>3.4</v>
       </c>
       <c r="AI15" t="n">
-        <v>4</v>
+        <v>1.25</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.36</v>
+        <v>4.75</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45729.60416666666</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.09</v>
+        <v>2.36</v>
       </c>
       <c r="M16" t="n">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>2.36</v>
+        <v>2.99</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['33']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.83</v>
       </c>
-      <c r="Q16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['15']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>2</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45729.60416666666</v>
@@ -2578,19 +2578,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Caldiero Terme</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
         <v>1.57</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="N17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="AH17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI17" t="n">
         <v>2</v>
       </c>
-      <c r="Q17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['6', '62', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['70']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45729.60416666666</v>
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Caldiero Terme</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
         <v>1</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,22 +2733,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.52</v>
+        <v>1.57</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.87</v>
       </c>
       <c r="N18" t="n">
-        <v>2.78</v>
+        <v>5.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
         <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="R18" t="n">
         <v>1.5</v>
@@ -2766,50 +2766,50 @@
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="X18" t="n">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC18" t="n">
         <v>2.1</v>
       </c>
-      <c r="Z18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['6', '62', '90+3']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['25', '50']</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.58</v>
+        <v>2.35</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45729.60416666666</v>
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Raed</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>3.63</v>
       </c>
       <c r="N19" t="n">
-        <v>8.460000000000001</v>
+        <v>5.02</v>
       </c>
       <c r="O19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.62</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X19" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z19" t="n">
+      <c r="AD19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['27', '60', '65']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>2.75</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['55', '90+11']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>['81']</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>3.6</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45729.66666666666</v>
@@ -3094,22 +3094,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Raed</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.68</v>
+        <v>1.26</v>
       </c>
       <c r="M21" t="n">
-        <v>3.63</v>
+        <v>6</v>
       </c>
       <c r="N21" t="n">
-        <v>5.02</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.85</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="R21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X21" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['55', '90+11']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI21" t="n">
         <v>1.3</v>
       </c>
-      <c r="S21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['27', '60', '65']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['82']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45729.66666666666</v>
@@ -3352,91 +3352,91 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V23" t="n">
         <v>1</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="M23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="O23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.03</v>
-      </c>
       <c r="W23" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="X23" t="n">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AC23" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['41', '65']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45729.69791666666</v>
@@ -3481,16 +3481,16 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>2.27</v>
       </c>
       <c r="M24" t="n">
-        <v>3.94</v>
+        <v>3.01</v>
       </c>
       <c r="N24" t="n">
-        <v>7.9</v>
+        <v>3.38</v>
       </c>
       <c r="O24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>7.5</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z24" t="n">
         <v>1.5</v>
       </c>
-      <c r="S24" t="n">
+      <c r="AA24" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>2.5</v>
-      </c>
-      <c r="T24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>['80']</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>4.5</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45729.69791666666</v>
@@ -3610,16 +3610,16 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.98</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
-        <v>3.34</v>
+        <v>3.94</v>
       </c>
       <c r="N25" t="n">
-        <v>2.3</v>
+        <v>7.9</v>
       </c>
       <c r="O25" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="P25" t="n">
         <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>7.5</v>
       </c>
       <c r="R25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.44</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>['80']</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI25" t="n">
         <v>1.33</v>
       </c>
-      <c r="V25" t="n">
-        <v>1</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ25" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45729.69791666666</v>
@@ -3739,22 +3739,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3765,22 +3765,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.27</v>
+        <v>2.78</v>
       </c>
       <c r="M26" t="n">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>3.38</v>
+        <v>2.57</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P26" t="n">
         <v>1.91</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
         <v>1.53</v>
@@ -3789,59 +3789,59 @@
         <v>2.38</v>
       </c>
       <c r="T26" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U26" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V26" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="X26" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AA26" t="n">
-        <v>4.33</v>
+        <v>4.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
+          <t>['41', '65']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45729.69791666666</v>
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Vere United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>6.5</v>
       </c>
       <c r="M28" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="N28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O28" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X28" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['5', '39']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>3.6</v>
       </c>
-      <c r="O28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['32', '65', '80']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.73</v>
+        <v>5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2.5</v>
+        <v>1.18</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45729.72916666666</v>
@@ -4126,19 +4126,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="M29" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="N29" t="n">
-        <v>8.5</v>
+        <v>3.6</v>
       </c>
       <c r="O29" t="n">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="P29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>['32', '65', '80']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>2.5</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X29" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['29', '48', '90+2', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>['89']</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>3.4</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45729.72916666666</v>
@@ -4255,25 +4255,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vere United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G30" t="n">
+        <v>4</v>
+      </c>
+      <c r="H30" t="n">
         <v>1</v>
       </c>
-      <c r="H30" t="n">
-        <v>2</v>
-      </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="M30" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="N30" t="n">
-        <v>1.44</v>
+        <v>8.5</v>
       </c>
       <c r="O30" t="n">
-        <v>8.5</v>
+        <v>1.83</v>
       </c>
       <c r="P30" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.67</v>
+        <v>5.75</v>
       </c>
       <c r="R30" t="n">
         <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="T30" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="U30" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W30" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X30" t="n">
-        <v>4.75</v>
+        <v>4.45</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['29', '48', '90+2', '90+3']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['5', '39']</t>
+          <t>['89']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>3.6</v>
+        <v>1.05</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="AI30" t="n">
-        <v>5</v>
+        <v>1.38</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.18</v>
+        <v>3.4</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45729.72916666666</v>
